--- a/01_analyses_states/Ladakh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Ladakh/results/SoIB_summaries.xlsx
@@ -584,10 +584,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C8">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +682,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -690,7 +690,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -698,7 +698,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +727,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -792,16 +792,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="D2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -812,13 +812,13 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D3">
         <v>20</v>
       </c>
       <c r="E3">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
     </row>
   </sheetData>
